--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/HESSEN_Datenbank/after_conversion_hessen_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/HESSEN_Datenbank/after_conversion_hessen_mapped_readable.xlsx
@@ -3526,7 +3526,7 @@
     <t>Sand and Gravel</t>
   </si>
   <si>
-    <t>Pelite</t>
+    <t>Claystone</t>
   </si>
   <si>
     <t>Slate</t>
@@ -25623,7 +25623,7 @@
         <v>920</v>
       </c>
       <c r="F321" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G321" t="s">
         <v>1189</v>
@@ -25679,7 +25679,7 @@
         <v>920</v>
       </c>
       <c r="F322" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G322" t="s">
         <v>1189</v>
@@ -25735,7 +25735,7 @@
         <v>921</v>
       </c>
       <c r="F323" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G323" t="s">
         <v>1189</v>
@@ -25806,7 +25806,7 @@
         <v>921</v>
       </c>
       <c r="F324" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G324" t="s">
         <v>1189</v>
@@ -25877,7 +25877,7 @@
         <v>919</v>
       </c>
       <c r="F325" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G325" t="s">
         <v>1189</v>
@@ -25933,7 +25933,7 @@
         <v>919</v>
       </c>
       <c r="F326" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G326" t="s">
         <v>1189</v>
@@ -25989,7 +25989,7 @@
         <v>922</v>
       </c>
       <c r="F327" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G327" t="s">
         <v>1189</v>
@@ -26045,7 +26045,7 @@
         <v>922</v>
       </c>
       <c r="F328" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G328" t="s">
         <v>1189</v>
@@ -26101,7 +26101,7 @@
         <v>922</v>
       </c>
       <c r="F329" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G329" t="s">
         <v>1189</v>
@@ -26151,7 +26151,7 @@
         <v>922</v>
       </c>
       <c r="F330" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G330" t="s">
         <v>1189</v>
@@ -26201,7 +26201,7 @@
         <v>922</v>
       </c>
       <c r="F331" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G331" t="s">
         <v>1189</v>
@@ -26272,7 +26272,7 @@
         <v>922</v>
       </c>
       <c r="F332" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G332" t="s">
         <v>1189</v>
@@ -26343,7 +26343,7 @@
         <v>923</v>
       </c>
       <c r="F333" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G333" t="s">
         <v>1189</v>
@@ -26414,7 +26414,7 @@
         <v>923</v>
       </c>
       <c r="F334" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G334" t="s">
         <v>1189</v>
@@ -26485,7 +26485,7 @@
         <v>923</v>
       </c>
       <c r="F335" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G335" t="s">
         <v>1189</v>
@@ -26517,7 +26517,7 @@
         <v>923</v>
       </c>
       <c r="F336" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G336" t="s">
         <v>1189</v>
@@ -26549,7 +26549,7 @@
         <v>923</v>
       </c>
       <c r="F337" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G337" t="s">
         <v>1189</v>
@@ -26629,7 +26629,7 @@
         <v>923</v>
       </c>
       <c r="F338" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G338" t="s">
         <v>1189</v>
@@ -26709,7 +26709,7 @@
         <v>923</v>
       </c>
       <c r="F339" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G339" t="s">
         <v>1189</v>
@@ -26765,7 +26765,7 @@
         <v>923</v>
       </c>
       <c r="F340" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G340" t="s">
         <v>1189</v>
@@ -26821,7 +26821,7 @@
         <v>923</v>
       </c>
       <c r="F341" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G341" t="s">
         <v>1189</v>
@@ -26910,7 +26910,7 @@
         <v>923</v>
       </c>
       <c r="F342" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G342" t="s">
         <v>1189</v>
@@ -26999,7 +26999,7 @@
         <v>922</v>
       </c>
       <c r="F343" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G343" t="s">
         <v>1189</v>
@@ -27055,7 +27055,7 @@
         <v>922</v>
       </c>
       <c r="F344" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G344" t="s">
         <v>1189</v>
@@ -27111,7 +27111,7 @@
         <v>924</v>
       </c>
       <c r="F345" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G345" t="s">
         <v>1189</v>
@@ -27167,7 +27167,7 @@
         <v>924</v>
       </c>
       <c r="F346" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G346" t="s">
         <v>1189</v>
@@ -27223,7 +27223,7 @@
         <v>925</v>
       </c>
       <c r="F347" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G347" t="s">
         <v>1189</v>
@@ -27279,7 +27279,7 @@
         <v>925</v>
       </c>
       <c r="F348" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G348" t="s">
         <v>1189</v>
@@ -27335,7 +27335,7 @@
         <v>879</v>
       </c>
       <c r="F349" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G349" t="s">
         <v>1189</v>
@@ -27391,7 +27391,7 @@
         <v>879</v>
       </c>
       <c r="F350" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G350" t="s">
         <v>1189</v>
@@ -27447,7 +27447,7 @@
         <v>886</v>
       </c>
       <c r="F351" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G351" t="s">
         <v>1189</v>
@@ -27503,7 +27503,7 @@
         <v>886</v>
       </c>
       <c r="F352" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G352" t="s">
         <v>1189</v>
@@ -27559,7 +27559,7 @@
         <v>926</v>
       </c>
       <c r="F353" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G353" t="s">
         <v>1189</v>
@@ -27615,7 +27615,7 @@
         <v>926</v>
       </c>
       <c r="F354" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G354" t="s">
         <v>1189</v>
@@ -27671,7 +27671,7 @@
         <v>927</v>
       </c>
       <c r="F355" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G355" t="s">
         <v>1189</v>
@@ -27721,7 +27721,7 @@
         <v>927</v>
       </c>
       <c r="F356" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G356" t="s">
         <v>1189</v>
@@ -27771,7 +27771,7 @@
         <v>879</v>
       </c>
       <c r="F357" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G357" t="s">
         <v>1189</v>
@@ -27827,7 +27827,7 @@
         <v>879</v>
       </c>
       <c r="F358" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G358" t="s">
         <v>1189</v>
@@ -27883,7 +27883,7 @@
         <v>928</v>
       </c>
       <c r="F359" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G359" t="s">
         <v>1189</v>
@@ -27951,7 +27951,7 @@
         <v>928</v>
       </c>
       <c r="F360" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G360" t="s">
         <v>1189</v>
@@ -28019,7 +28019,7 @@
         <v>928</v>
       </c>
       <c r="F361" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G361" t="s">
         <v>1189</v>
@@ -28075,7 +28075,7 @@
         <v>928</v>
       </c>
       <c r="F362" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G362" t="s">
         <v>1189</v>
@@ -28131,7 +28131,7 @@
         <v>928</v>
       </c>
       <c r="F363" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G363" t="s">
         <v>1189</v>
@@ -28199,7 +28199,7 @@
         <v>928</v>
       </c>
       <c r="F364" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G364" t="s">
         <v>1189</v>
@@ -28267,7 +28267,7 @@
         <v>928</v>
       </c>
       <c r="F365" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G365" t="s">
         <v>1189</v>
@@ -28299,7 +28299,7 @@
         <v>928</v>
       </c>
       <c r="F366" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G366" t="s">
         <v>1189</v>
@@ -28331,7 +28331,7 @@
         <v>928</v>
       </c>
       <c r="F367" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G367" t="s">
         <v>1189</v>
@@ -28411,7 +28411,7 @@
         <v>928</v>
       </c>
       <c r="F368" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G368" t="s">
         <v>1189</v>
@@ -28491,7 +28491,7 @@
         <v>928</v>
       </c>
       <c r="F369" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G369" t="s">
         <v>1189</v>
@@ -28547,7 +28547,7 @@
         <v>928</v>
       </c>
       <c r="F370" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G370" t="s">
         <v>1189</v>
@@ -28603,7 +28603,7 @@
         <v>928</v>
       </c>
       <c r="F371" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G371" t="s">
         <v>1189</v>
@@ -28692,7 +28692,7 @@
         <v>928</v>
       </c>
       <c r="F372" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G372" t="s">
         <v>1189</v>
@@ -28781,7 +28781,7 @@
         <v>929</v>
       </c>
       <c r="F373" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G373" t="s">
         <v>1189</v>
@@ -28855,7 +28855,7 @@
         <v>929</v>
       </c>
       <c r="F374" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G374" t="s">
         <v>1189</v>
@@ -28929,7 +28929,7 @@
         <v>929</v>
       </c>
       <c r="F375" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G375" t="s">
         <v>1189</v>
@@ -28985,7 +28985,7 @@
         <v>929</v>
       </c>
       <c r="F376" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G376" t="s">
         <v>1189</v>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/HESSEN_Datenbank/after_conversion_hessen_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/HESSEN_Datenbank/after_conversion_hessen_mapped_readable.xlsx
@@ -3544,7 +3544,7 @@
     <t>Greenschist</t>
   </si>
   <si>
-    <t>Halite</t>
+    <t>Salt</t>
   </si>
   <si>
     <t>Limestone</t>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/HESSEN_Datenbank/after_conversion_hessen_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/HESSEN_Datenbank/after_conversion_hessen_mapped_readable.xlsx
@@ -4692,6 +4692,9 @@
       <c r="AB2">
         <v>398.1564460376392</v>
       </c>
+      <c r="AD2">
+        <v>6</v>
+      </c>
     </row>
     <row r="3" spans="1:31">
       <c r="A3" t="s">
@@ -4742,6 +4745,9 @@
       <c r="X3">
         <v>0.1790670606142</v>
       </c>
+      <c r="AD3">
+        <v>6</v>
+      </c>
     </row>
     <row r="4" spans="1:31">
       <c r="A4" t="s">
@@ -4809,6 +4815,9 @@
       </c>
       <c r="AA4">
         <v>0.0564471517573611</v>
+      </c>
+      <c r="AD4">
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:31">
